--- a/docs/Mapping_casi_uso/trascrizioni/Trascr_010.xlsx
+++ b/docs/Mapping_casi_uso/trascrizioni/Trascr_010.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1057" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1064" uniqueCount="153">
   <si>
     <t>Sezione</t>
   </si>
@@ -303,6 +303,12 @@
   </si>
   <si>
     <t>evento.intestatari[0]</t>
+  </si>
+  <si>
+    <t>Residenza al momento dell'evento originario</t>
+  </si>
+  <si>
+    <t>residenzaOriginaria</t>
   </si>
   <si>
     <t>Atto nascita intestatario</t>
@@ -523,7 +529,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H151"/>
+  <dimension ref="A1:H152"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.59765625" customWidth="true" bestFit="true"/>
@@ -3435,19 +3441,19 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B127" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="B127" s="2" t="s">
+      <c r="C127" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E127" s="2" t="s">
         <v>98</v>
-      </c>
-      <c r="C127" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D127" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="E127" s="2" t="s">
-        <v>100</v>
       </c>
       <c r="F127" s="2" t="s">
         <v>10</v>
@@ -3458,16 +3464,16 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B128" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D128" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="C128" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D128" s="2" t="s">
-        <v>99</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>102</v>
@@ -3481,7 +3487,7 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>103</v>
@@ -3490,7 +3496,7 @@
         <v>9</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>104</v>
@@ -3504,7 +3510,7 @@
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B130" s="2" t="s">
         <v>105</v>
@@ -3513,7 +3519,7 @@
         <v>9</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>106</v>
@@ -3527,7 +3533,7 @@
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B131" s="2" t="s">
         <v>107</v>
@@ -3536,7 +3542,7 @@
         <v>9</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>108</v>
@@ -3550,7 +3556,7 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B132" s="2" t="s">
         <v>109</v>
@@ -3559,7 +3565,7 @@
         <v>9</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>110</v>
@@ -3573,7 +3579,7 @@
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B133" s="2" t="s">
         <v>111</v>
@@ -3582,10 +3588,10 @@
         <v>9</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>20</v>
+        <v>112</v>
       </c>
       <c r="F133" s="2" t="s">
         <v>10</v>
@@ -3596,19 +3602,19 @@
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>113</v>
+        <v>20</v>
       </c>
       <c r="F134" s="2" t="s">
         <v>10</v>
@@ -3619,7 +3625,7 @@
     </row>
     <row r="135">
       <c r="A135" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B135" s="2" t="s">
         <v>114</v>
@@ -3628,10 +3634,10 @@
         <v>9</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>23</v>
+        <v>115</v>
       </c>
       <c r="F135" s="2" t="s">
         <v>10</v>
@@ -3642,19 +3648,19 @@
     </row>
     <row r="136">
       <c r="A136" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>116</v>
+        <v>23</v>
       </c>
       <c r="F136" s="2" t="s">
         <v>10</v>
@@ -3665,7 +3671,7 @@
     </row>
     <row r="137">
       <c r="A137" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B137" s="2" t="s">
         <v>117</v>
@@ -3674,7 +3680,7 @@
         <v>13</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E137" s="2" t="s">
         <v>118</v>
@@ -3688,7 +3694,7 @@
     </row>
     <row r="138">
       <c r="A138" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B138" s="2" t="s">
         <v>119</v>
@@ -3697,7 +3703,7 @@
         <v>13</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>120</v>
@@ -3711,16 +3717,16 @@
     </row>
     <row r="139">
       <c r="A139" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B139" s="2" t="s">
         <v>121</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E139" s="2" t="s">
         <v>122</v>
@@ -3734,19 +3740,19 @@
     </row>
     <row r="140">
       <c r="A140" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B140" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="B140" s="2" t="s">
+      <c r="C140" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D140" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E140" s="2" t="s">
         <v>124</v>
-      </c>
-      <c r="C140" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D140" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E140" s="2" t="s">
-        <v>126</v>
       </c>
       <c r="F140" s="2" t="s">
         <v>10</v>
@@ -3757,16 +3763,16 @@
     </row>
     <row r="141">
       <c r="A141" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B141" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D141" s="2" t="s">
         <v>127</v>
-      </c>
-      <c r="C141" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D141" s="2" t="s">
-        <v>125</v>
       </c>
       <c r="E141" s="2" t="s">
         <v>128</v>
@@ -3780,7 +3786,7 @@
     </row>
     <row r="142">
       <c r="A142" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B142" s="2" t="s">
         <v>129</v>
@@ -3789,7 +3795,7 @@
         <v>9</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E142" s="2" t="s">
         <v>130</v>
@@ -3803,19 +3809,19 @@
     </row>
     <row r="143">
       <c r="A143" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>53</v>
+        <v>131</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F143" s="2" t="s">
         <v>10</v>
@@ -3826,16 +3832,16 @@
     </row>
     <row r="144">
       <c r="A144" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>132</v>
+        <v>53</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E144" s="2" t="s">
         <v>133</v>
@@ -3849,16 +3855,16 @@
     </row>
     <row r="145">
       <c r="A145" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B145" s="2" t="s">
         <v>134</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E145" s="2" t="s">
         <v>135</v>
@@ -3872,7 +3878,7 @@
     </row>
     <row r="146">
       <c r="A146" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B146" s="2" t="s">
         <v>136</v>
@@ -3881,7 +3887,7 @@
         <v>13</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E146" s="2" t="s">
         <v>137</v>
@@ -3895,19 +3901,19 @@
     </row>
     <row r="147">
       <c r="A147" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B147" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="B147" s="2" t="s">
+      <c r="C147" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D147" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="E147" s="2" t="s">
         <v>139</v>
-      </c>
-      <c r="C147" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D147" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="E147" s="2" t="s">
-        <v>141</v>
       </c>
       <c r="F147" s="2" t="s">
         <v>10</v>
@@ -3918,16 +3924,16 @@
     </row>
     <row r="148">
       <c r="A148" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B148" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C148" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D148" s="2" t="s">
         <v>142</v>
-      </c>
-      <c r="C148" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D148" s="2" t="s">
-        <v>140</v>
       </c>
       <c r="E148" s="2" t="s">
         <v>143</v>
@@ -3941,7 +3947,7 @@
     </row>
     <row r="149">
       <c r="A149" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B149" s="2" t="s">
         <v>144</v>
@@ -3950,7 +3956,7 @@
         <v>9</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E149" s="2" t="s">
         <v>145</v>
@@ -3964,19 +3970,19 @@
     </row>
     <row r="150">
       <c r="A150" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B150" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="B150" s="2" t="s">
+      <c r="C150" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D150" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E150" s="2" t="s">
         <v>147</v>
-      </c>
-      <c r="C150" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D150" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="E150" s="2" t="s">
-        <v>148</v>
       </c>
       <c r="F150" s="2" t="s">
         <v>10</v>
@@ -3987,16 +3993,16 @@
     </row>
     <row r="151">
       <c r="A151" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B151" s="2" t="s">
         <v>149</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E151" s="2" t="s">
         <v>150</v>
@@ -4005,6 +4011,29 @@
         <v>10</v>
       </c>
       <c r="G151" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D152" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E152" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="F152" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G152" s="2" t="s">
         <v>21</v>
       </c>
     </row>
